--- a/modelo_contratos.xlsx
+++ b/modelo_contratos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E044626-556A-4946-89D0-32A2DA5035EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C40989B-7C86-4611-B2FA-EFB6DA535B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Nº Contrato</t>
   </si>
@@ -88,7 +88,19 @@
     <t>Marcos Brumatti</t>
   </si>
   <si>
-    <t>Portaria nº 005/2022</t>
+    <t>010/2026</t>
+  </si>
+  <si>
+    <t>Estudo tecnico e projeto</t>
+  </si>
+  <si>
+    <t>WM Consultoria</t>
+  </si>
+  <si>
+    <t>005/2026</t>
+  </si>
+  <si>
+    <t>005/2022</t>
   </si>
 </sst>
 </file>
@@ -159,13 +171,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -562,10 +575,39 @@
         <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3">
         <v>44696</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46143</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F4" s="4">
+        <v>59000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3">
+        <v>46188</v>
       </c>
     </row>
   </sheetData>
